--- a/20251229_new_progress/Code/paper_data_newdata/main_paper_results/05_category_level_interpretation/outputs/category_level_interpretation.xlsx
+++ b/20251229_new_progress/Code/paper_data_newdata/main_paper_results/05_category_level_interpretation/outputs/category_level_interpretation.xlsx
@@ -20,10 +20,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ReadMe'!$A$1:$B$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CategorySummaryLong'!$A$1:$D$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CategoryNarrative'!$A$1:$I$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'StableDomains'!$A$1:$J$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'CandidateInteractions'!$A$1:$M$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'StableDomains'!$A$1:$J$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'CandidateInteractions'!$A$1:$M$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'InterpersonalInterpretation'!$A$1:$I$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'SharedTop20Source'!$A$1:$J$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'SharedTop20Source'!$A$1:$J$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'FigureIndex'!$A$1:$C$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -592,10 +592,10 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>42.2386984223301</v>
+        <v>44.72565386755705</v>
       </c>
     </row>
     <row r="3">
@@ -613,7 +613,7 @@
         <v>5</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>18.48263046116505</v>
+        <v>20.09794101279911</v>
       </c>
     </row>
     <row r="4">
@@ -631,7 +631,7 @@
         <v>2</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>8.163304004854369</v>
+        <v>8.928213689482472</v>
       </c>
     </row>
     <row r="5">
@@ -646,10 +646,10 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>4.805066747572814</v>
+        <v>8.558708959376739</v>
       </c>
     </row>
     <row r="6">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>5.838516383495145</v>
+        <v>3.025041736227045</v>
       </c>
     </row>
     <row r="7">
@@ -685,7 +685,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.345494538834951</v>
+        <v>6.096828046744574</v>
       </c>
     </row>
     <row r="8">
@@ -703,7 +703,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.818492111650485</v>
+        <v>1.903171953255426</v>
       </c>
     </row>
     <row r="9">
@@ -721,7 +721,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>37.04730313082199</v>
+        <v>36.59733477399605</v>
       </c>
     </row>
     <row r="10">
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>24.7557595310583</v>
+        <v>26.38663785341257</v>
       </c>
     </row>
     <row r="11">
@@ -757,7 +757,7 @@
         <v>3</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>10.15131549052574</v>
+        <v>10.04412029533586</v>
       </c>
     </row>
     <row r="12">
@@ -775,7 +775,7 @@
         <v>4</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>9.469714181851227</v>
+        <v>9.485863497208717</v>
       </c>
     </row>
     <row r="13">
@@ -789,12 +789,8 @@
           <t>Interpersonal Network</t>
         </is>
       </c>
-      <c r="C13" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>2.190212205207434</v>
-      </c>
+      <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -811,7 +807,7 @@
         <v>1</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>6.602444676693779</v>
+        <v>6.514496668467496</v>
       </c>
     </row>
     <row r="15">
@@ -829,7 +825,7 @@
         <v>1</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>3.907847503067205</v>
+        <v>3.876283090221502</v>
       </c>
     </row>
   </sheetData>
@@ -912,22 +908,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>42.2386984223301</v>
+        <v>44.72565386755705</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>37.04730313082199</v>
+        <v>36.59733477399605</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>39.64300077657605</v>
+        <v>40.66149432077655</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>-5.191395291508115</v>
+        <v>-8.128319093560997</v>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
@@ -950,19 +946,19 @@
         <v>5</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>18.48263046116505</v>
+        <v>20.09794101279911</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>24.7557595310583</v>
+        <v>26.38663785341257</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>21.61919499611167</v>
+        <v>23.24228943310584</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>6.273129069893248</v>
+        <v>6.288696840613458</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
@@ -985,19 +981,19 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>8.163304004854369</v>
+        <v>8.928213689482472</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>10.15131549052574</v>
+        <v>10.04412029533586</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>9.157309747690054</v>
+        <v>9.486166992409167</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1.98801148567137</v>
+        <v>1.115906605853388</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
@@ -1017,22 +1013,22 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>4.805066747572814</v>
+        <v>8.558708959376739</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>9.469714181851227</v>
+        <v>9.485863497208717</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>7.137390464712021</v>
+        <v>9.022286228292728</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>4.664647434278413</v>
+        <v>0.9271545378319779</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
@@ -1052,22 +1048,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>5.838516383495145</v>
+        <v>3.025041736227045</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>2.190212205207434</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>4.01436429435129</v>
+        <v>1.512520868113522</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>-3.648304178287711</v>
+        <v>-3.025041736227045</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -1090,19 +1086,19 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>5.345494538834951</v>
+        <v>6.096828046744574</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>6.602444676693779</v>
+        <v>6.514496668467496</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>5.973969607764365</v>
+        <v>6.305662357606035</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1.256950137858828</v>
+        <v>0.417668621722922</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
@@ -1125,19 +1121,19 @@
         <v>1</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1.818492111650485</v>
+        <v>1.903171953255426</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>3.907847503067205</v>
+        <v>3.876283090221502</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>2.863169807358845</v>
+        <v>2.889727521738464</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>2.08935539141672</v>
+        <v>1.973111136966076</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
@@ -1162,7 +1158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -1236,22 +1232,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>42.2386984223301</v>
+        <v>44.72565386755705</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>37.04730313082199</v>
+        <v>36.59733477399605</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>39.64300077657605</v>
+        <v>40.66149432077655</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>-5.191395291508115</v>
+        <v>-8.128319093560997</v>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
@@ -1279,19 +1275,19 @@
         <v>5</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>18.48263046116505</v>
+        <v>20.09794101279911</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>24.7557595310583</v>
+        <v>26.38663785341257</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>21.61919499611167</v>
+        <v>23.24228943310584</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>6.273129069893248</v>
+        <v>6.288696840613458</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
@@ -1319,19 +1315,19 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>8.163304004854369</v>
+        <v>8.928213689482472</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>10.15131549052574</v>
+        <v>10.04412029533586</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>9.157309747690054</v>
+        <v>9.486166992409167</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1.98801148567137</v>
+        <v>1.115906605853388</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
@@ -1356,22 +1352,22 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>4.805066747572814</v>
+        <v>8.558708959376739</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>9.469714181851227</v>
+        <v>9.485863497208717</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>7.137390464712021</v>
+        <v>9.022286228292728</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>4.664647434278413</v>
+        <v>0.9271545378319779</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
@@ -1399,19 +1395,19 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>5.345494538834951</v>
+        <v>6.096828046744574</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>6.602444676693779</v>
+        <v>6.514496668467496</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>5.973969607764365</v>
+        <v>6.305662357606035</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1.256950137858828</v>
+        <v>0.417668621722922</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -1432,35 +1428,35 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Interpersonal Network</t>
+          <t>Delinquency / Risk Behavior</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>5.838516383495145</v>
+        <v>1.903171953255426</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2.190212205207434</v>
+        <v>3.876283090221502</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>4.01436429435129</v>
+        <v>2.889727521738464</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>-3.648304178287711</v>
+        <v>1.973111136966076</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Present but not dominant; weaker in longitudinal prediction.</t>
+          <t>Smaller domain but appears in both tasks.</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Use as evidence that peer-network structure adds limited explanatory weight compared with individual-level domains.</t>
+          <t>Use as secondary behavioral-risk context.</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1469,48 +1465,8 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Delinquency / Risk Behavior</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>1.818492111650485</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>3.907847503067205</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>2.863169807358845</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>2.08935539141672</v>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>Smaller domain but appears in both tasks.</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>Use as secondary behavioral-risk context.</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>Low stable domain</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J8"/>
+  <autoFilter ref="A1:J7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1521,7 +1477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1631,10 +1587,10 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>-0.3827</v>
+        <v>-0.3822</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>17.38992138864906</v>
+        <v>17.20691518098326</v>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
@@ -1655,7 +1611,7 @@
         </is>
       </c>
       <c r="L2" s="3" t="n">
-        <v>25.38992138864906</v>
+        <v>25.20691518098326</v>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
@@ -1688,10 +1644,10 @@
         <v>1</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>-0.772</v>
+        <v>-0.7557</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>14.63895631067961</v>
+        <v>16.82136894824708</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
@@ -1712,7 +1668,7 @@
         </is>
       </c>
       <c r="L3" s="3" t="n">
-        <v>22.63895631067961</v>
+        <v>24.82136894824708</v>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
@@ -1745,10 +1701,10 @@
         <v>2</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.6325</v>
+        <v>0.6155</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>11.99370449029126</v>
+        <v>13.70061213133</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
@@ -1769,7 +1725,7 @@
         </is>
       </c>
       <c r="L4" s="3" t="n">
-        <v>19.99370449029126</v>
+        <v>21.70061213133</v>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
@@ -1802,10 +1758,10 @@
         <v>2</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.2402</v>
+        <v>0.2401</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>10.91470895624119</v>
+        <v>10.80947235728435</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
@@ -1826,7 +1782,7 @@
         </is>
       </c>
       <c r="L5" s="3" t="n">
-        <v>18.91470895624119</v>
+        <v>18.80947235728435</v>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
@@ -1859,10 +1815,10 @@
         <v>3</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-0.3937</v>
+        <v>-0.3603</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>7.465488470873787</v>
+        <v>8.020033388981638</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -1883,7 +1839,7 @@
         </is>
       </c>
       <c r="L6" s="3" t="n">
-        <v>15.46548847087379</v>
+        <v>16.02003338898164</v>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
@@ -1916,10 +1872,10 @@
         <v>8</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>-0.2497</v>
+        <v>-0.2233</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>4.734905946601941</v>
+        <v>4.970506399554814</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
@@ -1940,7 +1896,7 @@
         </is>
       </c>
       <c r="L7" s="3" t="n">
-        <v>12.73490594660194</v>
+        <v>12.97050639955481</v>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
@@ -1973,10 +1929,10 @@
         <v>8</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>-0.0987</v>
+        <v>-0.0969</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>4.484936611078292</v>
+        <v>4.36250675310643</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
@@ -1997,7 +1953,7 @@
         </is>
       </c>
       <c r="L8" s="3" t="n">
-        <v>12.48493661107829</v>
+        <v>12.36250675310643</v>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
@@ -2033,7 +1989,7 @@
         <v>-0.09370000000000001</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>4.257736174853456</v>
+        <v>4.218440482622007</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
@@ -2054,7 +2010,7 @@
         </is>
       </c>
       <c r="L9" s="3" t="n">
-        <v>12.25773617485346</v>
+        <v>12.21844048262201</v>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
@@ -2087,10 +2043,10 @@
         <v>4</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.3371</v>
+        <v>0.3186</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>6.392217839805825</v>
+        <v>7.091819699499166</v>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
@@ -2111,7 +2067,7 @@
         </is>
       </c>
       <c r="L10" s="3" t="n">
-        <v>11.39221783980583</v>
+        <v>12.09181969949917</v>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
@@ -2122,36 +2078,36 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>W2 -&gt; W3</t>
+          <t>W2 -&gt; W2</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Online Perspective Seeking</t>
+          <t>Family Cohesion and Support (Family Functioning)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>v26_B</t>
+          <t>v5</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Online / Digital Life</t>
+          <t>Family / Parenting</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.1303</v>
+        <v>-0.2733</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>5.920843368019265</v>
+        <v>6.083472454090151</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="I11" s="3" t="b">
@@ -2159,20 +2115,20 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Digital-life covariate or mechanism</t>
+          <t>Secondary contextual moderator</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Digital-life mechanism/covariate; use carefully with High Online Activity to avoid redundancy.</t>
+          <t>Candidate contextual protective moderator.</t>
         </is>
       </c>
       <c r="L11" s="3" t="n">
-        <v>10.92084336801927</v>
+        <v>11.08347245409015</v>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>v26_4;v26_5;v26_6</t>
+          <t>v5_1;v5_2;v5_3;v5_4;v5_5;v5_6</t>
         </is>
       </c>
     </row>
@@ -2184,12 +2140,12 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Problematic Internet Use and Internet Dependence</t>
+          <t>Online Perspective Seeking</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>v28</t>
+          <t>v26_B</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -2198,13 +2154,13 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.1206</v>
+        <v>0.1293</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>5.480074521743081</v>
+        <v>5.821177741761211</v>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
@@ -2221,51 +2177,51 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Digital risk mechanism; usually model as exposure/covariate rather than protective moderator.</t>
+          <t>Digital-life mechanism/covariate; use carefully with High Online Activity to avoid redundancy.</t>
         </is>
       </c>
       <c r="L12" s="3" t="n">
-        <v>10.48007452174308</v>
+        <v>10.82117774176121</v>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>v28_1;v28_2;v28_3;v28_4;v28_5;v28_6;v28_7;v28_8;v28_9;v28_10</t>
+          <t>v26_4;v26_5;v26_6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>W2 -&gt; W2</t>
+          <t>W2 -&gt; W3</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Family Cohesion and Support (Family Functioning)</t>
+          <t>Problematic Internet Use and Internet Dependence</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>v5</t>
+          <t>v28</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Family / Parenting</t>
+          <t>Online / Digital Life</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
         <v>5</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0.2887</v>
+        <v>0.1189</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>5.474438713592233</v>
+        <v>5.352962362686837</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="I13" s="3" t="b">
@@ -2273,20 +2229,20 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>Secondary contextual moderator</t>
+          <t>Digital-life covariate or mechanism</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Candidate contextual protective moderator.</t>
+          <t>Digital risk mechanism; usually model as exposure/covariate rather than protective moderator.</t>
         </is>
       </c>
       <c r="L13" s="3" t="n">
-        <v>10.47443871359223</v>
+        <v>10.35296236268684</v>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>v5_1;v5_2;v5_3;v5_4;v5_5;v5_6</t>
+          <t>v28_1;v28_2;v28_3;v28_4;v28_5;v28_6;v28_7;v28_8;v28_9;v28_10</t>
         </is>
       </c>
     </row>
@@ -2315,10 +2271,10 @@
         <v>6</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>-0.1167</v>
+        <v>-0.1157</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>5.302858181487707</v>
+        <v>5.208896092202414</v>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
@@ -2339,7 +2295,7 @@
         </is>
       </c>
       <c r="L14" s="3" t="n">
-        <v>10.30285818148771</v>
+        <v>10.20889609220241</v>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
@@ -2372,10 +2328,10 @@
         <v>7</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.2505</v>
+        <v>0.2314</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>4.750075849514563</v>
+        <v>5.150806900389538</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
@@ -2396,7 +2352,7 @@
         </is>
       </c>
       <c r="L15" s="3" t="n">
-        <v>9.750075849514563</v>
+        <v>10.15080690038954</v>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
@@ -2426,13 +2382,13 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.1535</v>
+        <v>0.1499</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>2.910725121359223</v>
+        <v>3.33667223149694</v>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
@@ -2453,7 +2409,7 @@
         </is>
       </c>
       <c r="L16" s="3" t="n">
-        <v>7.910725121359222</v>
+        <v>8.336672231496941</v>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
@@ -2464,32 +2420,32 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>W2 -&gt; W2</t>
+          <t>W2 -&gt; W3</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Parenting Practices and Parent-Child Interaction Quality (Support/Conflict/Monitoring)</t>
+          <t>Physical/Offline Bullying Victimization</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>v6</t>
+          <t>v34</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Family / Parenting</t>
+          <t>Bullying / Victimization</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.1418</v>
+        <v>0.0654</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>2.688865291262136</v>
+        <v>2.944354403025392</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
@@ -2501,56 +2457,56 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>Secondary contextual moderator</t>
+          <t>Risk-context moderator</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Secondary candidate.</t>
+          <t>Candidate risk-context interaction with High Online Activity.</t>
         </is>
       </c>
       <c r="L17" s="3" t="n">
-        <v>7.688865291262136</v>
+        <v>7.944354403025391</v>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>v6_1;v6_2;v6_3;v6_4;v6_5;v6_6;v6_7;v6_8;v6_9;v6_10</t>
+          <t>v34</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>W2 -&gt; W3</t>
+          <t>W2 -&gt; W2</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Perceived Effectiveness of School-based Digital/Technology Learning</t>
+          <t>Parenting Practices and Parent-Child Interaction Quality (Support/Conflict/Monitoring)</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>v49</t>
+          <t>v6</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Online / Digital Life</t>
+          <t>Family / Parenting</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>-0.0513</v>
+        <v>0.1278</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>2.331076475666833</v>
+        <v>2.844741235392321</v>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="I18" s="3" t="b">
@@ -2558,20 +2514,20 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>Digital-life covariate or mechanism</t>
+          <t>Secondary contextual moderator</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Digital-life mechanism/covariate; use carefully with High Online Activity to avoid redundancy.</t>
+          <t>Secondary candidate.</t>
         </is>
       </c>
       <c r="L18" s="3" t="n">
-        <v>7.331076475666833</v>
+        <v>7.844741235392322</v>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>v49</t>
+          <t>v6_1;v6_2;v6_3;v6_4;v6_5;v6_6;v6_7;v6_8;v6_9;v6_10</t>
         </is>
       </c>
     </row>
@@ -2583,12 +2539,12 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Cyberbullying Victimization (including Misinformation-related)</t>
+          <t>Physical/Offline Bullying Perpetration</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>v38</t>
+          <t>v36</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -2597,13 +2553,13 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0.0499</v>
+        <v>0.0506</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>2.267460353523878</v>
+        <v>2.278047902034936</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
@@ -2624,11 +2580,11 @@
         </is>
       </c>
       <c r="L19" s="3" t="n">
-        <v>7.267460353523878</v>
+        <v>7.278047902034936</v>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>v38</t>
+          <t>v36</t>
         </is>
       </c>
     </row>
@@ -2640,31 +2596,31 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Parenting Practices and Parent-Child Interaction Quality (Support/Conflict/Monitoring)</t>
+          <t>Perceived Effectiveness of School-based Digital/Technology Learning</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>v6</t>
+          <t>v49</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Family / Parenting</t>
+          <t>Online / Digital Life</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.0498</v>
+        <v>-0.0501</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>2.262916344799382</v>
+        <v>2.255537547271746</v>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="I20" s="3" t="b">
@@ -2672,20 +2628,20 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>Secondary contextual moderator</t>
+          <t>Digital-life covariate or mechanism</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Secondary candidate.</t>
+          <t>Digital-life mechanism/covariate; use carefully with High Online Activity to avoid redundancy.</t>
         </is>
       </c>
       <c r="L20" s="3" t="n">
-        <v>7.262916344799383</v>
+        <v>7.255537547271746</v>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>v6_1;v6_2;v6_3;v6_4;v6_5;v6_6;v6_7;v6_8;v6_9;v6_10</t>
+          <t>v49</t>
         </is>
       </c>
     </row>
@@ -2697,12 +2653,12 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Physical/Offline Bullying Perpetration</t>
+          <t>Cyberbullying Victimization (including Misinformation-related)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>v36</t>
+          <t>v38</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -2711,13 +2667,13 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.0491</v>
+        <v>0.0495</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>2.231108283727905</v>
+        <v>2.228525121555916</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
@@ -2738,11 +2694,11 @@
         </is>
       </c>
       <c r="L21" s="3" t="n">
-        <v>7.231108283727905</v>
+        <v>7.228525121555916</v>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>v36</t>
+          <t>v38</t>
         </is>
       </c>
     </row>
@@ -2768,13 +2724,13 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0.0999</v>
+        <v>0.1001</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>1.894341626213592</v>
+        <v>2.228158041179744</v>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
@@ -2795,7 +2751,7 @@
         </is>
       </c>
       <c r="L22" s="3" t="n">
-        <v>6.894341626213592</v>
+        <v>7.228158041179745</v>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
@@ -2806,36 +2762,36 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>W2 -&gt; W2</t>
+          <t>W2 -&gt; W3</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Perceived Effectiveness of School-based Digital/Technology Learning</t>
+          <t>Parenting Practices and Parent-Child Interaction Quality (Support/Conflict/Monitoring)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>v49</t>
+          <t>v6</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Online / Digital Life</t>
+          <t>Family / Parenting</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>-0.09429999999999999</v>
+        <v>0.0485</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1.788152305825243</v>
+        <v>2.183504412029534</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="I23" s="3" t="b">
@@ -2843,52 +2799,52 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>Digital-life covariate or mechanism</t>
+          <t>Secondary contextual moderator</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>Digital-life mechanism/covariate; use carefully with High Online Activity to avoid redundancy.</t>
+          <t>Secondary candidate.</t>
         </is>
       </c>
       <c r="L23" s="3" t="n">
-        <v>6.788152305825243</v>
+        <v>7.183504412029534</v>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>v49</t>
+          <t>v6_1;v6_2;v6_3;v6_4;v6_5;v6_6;v6_7;v6_8;v6_9;v6_10</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>W2 -&gt; W2</t>
+          <t>W2 -&gt; W3</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Social Awareness &amp; Relationship Skills</t>
+          <t>Cyberbullying Perpetration (including Misinformation-related)</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>v54_D</t>
+          <t>v40</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>SEL / Resilience</t>
+          <t>Bullying / Victimization</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.0452</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>1.776774878640777</v>
+        <v>2.034936070592473</v>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
@@ -2896,24 +2852,24 @@
         </is>
       </c>
       <c r="I24" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>Primary protective moderator</t>
+          <t>Risk-context moderator</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>Candidate SEL moderator; inspect item direction before final interpretation.</t>
+          <t>Candidate risk-context interaction with High Online Activity.</t>
         </is>
       </c>
       <c r="L24" s="3" t="n">
-        <v>4.776774878640778</v>
+        <v>7.034936070592472</v>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>v54_10;v54_11;v54_13;v54_14;v54_15</t>
+          <t>v40</t>
         </is>
       </c>
     </row>
@@ -2925,27 +2881,27 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Responsible Decision-Making</t>
+          <t>Perceived Effectiveness of School-based Digital/Technology Learning</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>v54_F</t>
+          <t>v49</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>SEL / Resilience</t>
+          <t>Online / Digital Life</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F25" s="3" t="n">
         <v>-0.0859</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1.628868325242719</v>
+        <v>1.912075681691709</v>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
@@ -2953,113 +2909,113 @@
         </is>
       </c>
       <c r="I25" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>Primary protective moderator</t>
+          <t>Digital-life covariate or mechanism</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>Strong candidate protective moderator for High Online Activity interaction.</t>
+          <t>Digital-life mechanism/covariate; use carefully with High Online Activity to avoid redundancy.</t>
         </is>
       </c>
       <c r="L25" s="3" t="n">
-        <v>4.628868325242719</v>
+        <v>6.912075681691709</v>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>v54_17;v54_19;v54_20</t>
+          <t>v49</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>W2 -&gt; W3</t>
+          <t>W2 -&gt; W2</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Real-life Self-Satisfaction</t>
+          <t>Physical/Offline Bullying Victimization</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>v25_B</t>
+          <t>v34</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Online / Digital Life</t>
+          <t>Bullying / Victimization</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-0.1018</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>4.625800881537693</v>
+        <v>1.742904841402337</v>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="I26" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>Digital-life covariate or mechanism</t>
+          <t>Risk-context moderator</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>Digital-life mechanism/covariate; use carefully with High Online Activity to avoid redundancy.</t>
+          <t>Candidate risk-context interaction with High Online Activity.</t>
         </is>
       </c>
       <c r="L26" s="3" t="n">
-        <v>4.625800881537693</v>
+        <v>6.742904841402337</v>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>v25_4;v25_5;v25_6</t>
+          <t>v34</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>W2 -&gt; W3</t>
+          <t>W2 -&gt; W2</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Selective Positive Sharing</t>
+          <t>Cyberbullying Perpetration (including Misinformation-related)</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>v23_A</t>
+          <t>v40</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Online / Digital Life</t>
+          <t>Bullying / Victimization</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.0562</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>3.289862316535647</v>
+        <v>1.250973845297718</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
@@ -3067,24 +3023,24 @@
         </is>
       </c>
       <c r="I27" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>Digital-life covariate or mechanism</t>
+          <t>Risk-context moderator</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>Digital-life mechanism/covariate; use carefully with High Online Activity to avoid redundancy.</t>
+          <t>Candidate risk-context interaction with High Online Activity.</t>
         </is>
       </c>
       <c r="L27" s="3" t="n">
-        <v>3.289862316535647</v>
+        <v>6.250973845297718</v>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>v23_1;v23_2;v23_3</t>
+          <t>v40</t>
         </is>
       </c>
     </row>
@@ -3096,12 +3052,12 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Online-Offline Discrepancy &amp; Immersion</t>
+          <t>Real-life Self-Satisfaction</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>v25_C</t>
+          <t>v25_B</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -3110,17 +3066,17 @@
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.0684</v>
+        <v>-0.1003</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>3.108101967555777</v>
+        <v>4.515577165496129</v>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="I28" s="3" t="b">
@@ -3137,11 +3093,11 @@
         </is>
       </c>
       <c r="L28" s="3" t="n">
-        <v>3.108101967555777</v>
+        <v>4.515577165496129</v>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>v25_7;v25_8;v25_9;v25_10;v25_11;v25_12;v25_13;v25_14;v25_15</t>
+          <t>v25_4;v25_5;v25_6</t>
         </is>
       </c>
     </row>
@@ -3153,31 +3109,31 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Online Coping and Support Seeking under Distress</t>
+          <t>Responsible Decision-Making</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>v22</t>
+          <t>v54_F</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Online / Digital Life</t>
+          <t>SEL / Resilience</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.1598</v>
+        <v>-0.0545</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>3.030188106796116</v>
+        <v>1.213132999443517</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="I29" s="3" t="b">
@@ -3185,20 +3141,20 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>Digital-life covariate or mechanism</t>
+          <t>Primary protective moderator</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>Digital-life mechanism/covariate; use carefully with High Online Activity to avoid redundancy.</t>
+          <t>Strong candidate protective moderator for High Online Activity interaction.</t>
         </is>
       </c>
       <c r="L29" s="3" t="n">
-        <v>3.030188106796116</v>
+        <v>4.213132999443517</v>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>v22_1;v22_2;v22_3;v22_4;v22_5;v22_6</t>
+          <t>v54_17;v54_19;v54_20</t>
         </is>
       </c>
     </row>
@@ -3210,27 +3166,27 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Physical/Offline Bullying Victimization</t>
+          <t>Selective Positive Sharing</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>v34</t>
+          <t>v23_A</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Bullying / Victimization</t>
+          <t>Online / Digital Life</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.065</v>
+        <v>0.074</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>2.953605670922888</v>
+        <v>3.331532504952278</v>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
@@ -3242,56 +3198,56 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>Risk-context moderator</t>
+          <t>Digital-life covariate or mechanism</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>Candidate risk-context interaction with High Online Activity.</t>
+          <t>Digital-life mechanism/covariate; use carefully with High Online Activity to avoid redundancy.</t>
         </is>
       </c>
       <c r="L30" s="3" t="n">
-        <v>2.953605670922888</v>
+        <v>3.331532504952278</v>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>v34</t>
+          <t>v23_1;v23_2;v23_3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>W2 -&gt; W3</t>
+          <t>W2 -&gt; W2</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Parental Involvement in Schooling and Academic Monitoring</t>
+          <t>Online Coping and Support Seeking under Distress</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>v19</t>
+          <t>v22</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Family / Parenting</t>
+          <t>Online / Digital Life</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-0.0569</v>
+        <v>0.1475</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>2.585540964238651</v>
+        <v>3.283249860879244</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="I31" s="3" t="b">
@@ -3299,37 +3255,37 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>Secondary contextual moderator</t>
+          <t>Digital-life covariate or mechanism</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>Candidate contextual protective moderator.</t>
+          <t>Digital-life mechanism/covariate; use carefully with High Online Activity to avoid redundancy.</t>
         </is>
       </c>
       <c r="L31" s="3" t="n">
-        <v>2.585540964238651</v>
+        <v>3.283249860879244</v>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>v19_1;v19_2;v19_3;v19_4;v19_5;v19_6;v19_7;v19_8;v19_9;v19_10</t>
+          <t>v22_1;v22_2;v22_3;v22_4;v22_5;v22_6</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>W2 -&gt; W2</t>
+          <t>W2 -&gt; W3</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Instant Response Pressure</t>
+          <t>Online-Offline Discrepancy &amp; Immersion</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>v27_B</t>
+          <t>v25_C</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -3341,14 +3297,14 @@
         <v>12</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>-0.133</v>
+        <v>0.0679</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>2.521996359223301</v>
+        <v>3.056906176841347</v>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="I32" s="3" t="b">
@@ -3365,47 +3321,47 @@
         </is>
       </c>
       <c r="L32" s="3" t="n">
-        <v>2.521996359223301</v>
+        <v>3.056906176841347</v>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>v27_4</t>
+          <t>v25_7;v25_8;v25_9;v25_10;v25_11;v25_12;v25_13;v25_14;v25_15</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>W2 -&gt; W3</t>
+          <t>W2 -&gt; W2</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Cyberbullying Perpetration (including Misinformation-related)</t>
+          <t>Instant Response Pressure</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>v40</t>
+          <t>v27_B</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Bullying / Victimization</t>
+          <t>Online / Digital Life</t>
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>0.0444</v>
+        <v>-0.1195</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>2.017539873676557</v>
+        <v>2.659988870339455</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="I33" s="3" t="b">
@@ -3413,25 +3369,139 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>Risk-context moderator</t>
+          <t>Digital-life covariate or mechanism</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>Candidate risk-context interaction with High Online Activity.</t>
+          <t>Digital-life mechanism/covariate; use carefully with High Online Activity to avoid redundancy.</t>
         </is>
       </c>
       <c r="L33" s="3" t="n">
-        <v>2.017539873676557</v>
+        <v>2.659988870339455</v>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>v40</t>
+          <t>v27_4</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>W2 -&gt; W3</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Parental Involvement in Schooling and Academic Monitoring</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>v19</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Family / Parenting</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>-0.0589</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>2.651719791103909</v>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>Secondary contextual moderator</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>Candidate contextual protective moderator.</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>2.651719791103909</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>v19_1;v19_2;v19_3;v19_4;v19_5;v19_6;v19_7;v19_8;v19_9;v19_10</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>W2 -&gt; W3</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Fear of Missing Out &amp; Social Anxiety</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>v27_A</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Online / Digital Life</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>0.0456</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>2.052944354403026</v>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>Digital-life covariate or mechanism</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>Digital-life mechanism/covariate; use carefully with High Online Activity to avoid redundancy.</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>2.052944354403026</v>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>v27_1;v27_2;v27_3</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M33"/>
+  <autoFilter ref="A1:M35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3451,7 +3521,7 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="41" customWidth="1" min="6" max="6"/>
-    <col width="57" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="77" customWidth="1" min="9" max="9"/>
   </cols>
@@ -3513,16 +3583,16 @@
         <v>12</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>9.801653519417474</v>
+        <v>5.19309961046188</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -3530,11 +3600,11 @@
         </is>
       </c>
       <c r="H2" s="3" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>Incoming Negative Nominations, Respondent-Class-Normalized; Outgoing Negative Nominations, Respondent-Class-Normalized; Received Network Valence, Respondent-Class-Normalized; Sent Network Valence, Respondent-Class-Normalized</t>
+          <t>Incoming Negative Nominations, Observed Count; Outgoing Negative Nominations, Observed Count; Received Network Valence, Observed; Reciprocal Friendship Ties, Observed Count; Sent Network Valence, Observed</t>
         </is>
       </c>
     </row>
@@ -3554,22 +3624,22 @@
         <v>8</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>3.171718089698732</v>
+        <v>3.952818296416352</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Reciprocal Friendship Ties, Respondent-Class-Normalized</t>
+          <t>Reciprocal Friendship Ties, Observed Count</t>
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Incoming Friendship Nominations, Respondent-Class-Normalized; Offline Total Nominations, Respondent-Class-Normalized; Outgoing Friendship Nominations, Respondent-Class-Normalized; Received Positive Tie Ratio; Received Network Valence, Respondent-Class-Normalized; Reciprocal Negative Ties, Respondent-Class-Normalized; Sent Positive Tie Ratio; Sent Network Valence, Respondent-Class-Normalized</t>
+          <t>Incoming Friendship Nominations, Observed Count; Offline Total Nominations, Observed Count; Outgoing Negative Nominations, Observed Count; Outgoing Friendship Nominations, Observed Count; Received Positive Tie Ratio; Received Network Valence, Observed; Reciprocal Negative Ties, Observed Count; Sent Positive Tie Ratio</t>
         </is>
       </c>
     </row>
@@ -3585,7 +3655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3672,19 +3742,19 @@
         <v>1</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>-0.772</v>
+        <v>-0.7557</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>14.63895631067961</v>
+        <v>16.82136894824708</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>-0.3827</v>
+        <v>-0.3822</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>17.38992138864906</v>
+        <v>17.20691518098326</v>
       </c>
       <c r="J2" s="3" t="b">
         <v>1</v>
@@ -3710,19 +3780,19 @@
         <v>2</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.6325</v>
+        <v>0.6155</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>11.99370449029126</v>
+        <v>13.70061213133</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.2402</v>
+        <v>0.2401</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>10.91470895624119</v>
+        <v>10.80947235728435</v>
       </c>
       <c r="J3" s="3" t="b">
         <v>1</v>
@@ -3748,10 +3818,10 @@
         <v>3</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>-0.3937</v>
+        <v>-0.3603</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>7.465488470873787</v>
+        <v>8.020033388981638</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>9</v>
@@ -3760,7 +3830,7 @@
         <v>-0.09370000000000001</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>4.257736174853456</v>
+        <v>4.218440482622007</v>
       </c>
       <c r="J4" s="3" t="b">
         <v>1</v>
@@ -3786,19 +3856,19 @@
         <v>4</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.3371</v>
+        <v>0.3186</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>6.392217839805825</v>
+        <v>7.091819699499166</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>5</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>0.1206</v>
+        <v>0.1189</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>5.480074521743081</v>
+        <v>5.352962362686837</v>
       </c>
       <c r="J5" s="3" t="b">
         <v>1</v>
@@ -3807,36 +3877,36 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>v5</t>
+          <t>v1_male</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Family Cohesion and Support (Family Functioning)</t>
+          <t>Gender: Male (vs Female)</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Family / Parenting</t>
+          <t>Demographic / Social Status</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
         <v>5</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>-0.2887</v>
+        <v>-0.2739</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>5.474438713592233</v>
+        <v>6.096828046744574</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.1167</v>
+        <v>-0.1447</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>5.302858181487707</v>
+        <v>6.514496668467496</v>
       </c>
       <c r="J6" s="3" t="b">
         <v>1</v>
@@ -3845,36 +3915,36 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>v1_male</t>
+          <t>v5</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Gender: Male (vs Female)</t>
+          <t>Family Cohesion and Support (Family Functioning)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Demographic / Social Status</t>
+          <t>Family / Parenting</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
         <v>6</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>-0.2819</v>
+        <v>-0.2733</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>5.345494538834951</v>
+        <v>6.083472454090151</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.1453</v>
+        <v>-0.1157</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>6.602444676693779</v>
+        <v>5.208896092202414</v>
       </c>
       <c r="J7" s="3" t="b">
         <v>1</v>
@@ -3900,19 +3970,19 @@
         <v>7</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0.2505</v>
+        <v>0.2314</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>4.750075849514563</v>
+        <v>5.150806900389538</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>4</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0.1303</v>
+        <v>0.1293</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>5.920843368019265</v>
+        <v>5.821177741761211</v>
       </c>
       <c r="J8" s="3" t="b">
         <v>1</v>
@@ -3938,19 +4008,19 @@
         <v>8</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>-0.2497</v>
+        <v>-0.2233</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>4.734905946601941</v>
+        <v>4.970506399554814</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>8</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>-0.0987</v>
+        <v>-0.0969</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>4.484936611078292</v>
+        <v>4.36250675310643</v>
       </c>
       <c r="J9" s="3" t="b">
         <v>1</v>
@@ -3973,22 +4043,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.1535</v>
+        <v>0.1499</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>2.910725121359223</v>
+        <v>3.33667223149694</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.0499</v>
+        <v>0.0495</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>2.267460353523878</v>
+        <v>2.228525121555916</v>
       </c>
       <c r="J10" s="3" t="b">
         <v>1</v>
@@ -4014,19 +4084,19 @@
         <v>11</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0.1418</v>
+        <v>0.1278</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>2.688865291262136</v>
+        <v>2.844741235392321</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.0498</v>
+        <v>0.0485</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>2.262916344799382</v>
+        <v>2.183504412029534</v>
       </c>
       <c r="J11" s="3" t="b">
         <v>1</v>
@@ -4049,22 +4119,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0.1001</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>2.228158041179744</v>
+      </c>
+      <c r="G12" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="E12" s="3" t="n">
-        <v>0.0999</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>1.894341626213592</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>18</v>
-      </c>
       <c r="H12" s="3" t="n">
-        <v>0.0491</v>
+        <v>0.0506</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>2.231108283727905</v>
+        <v>2.278047902034936</v>
       </c>
       <c r="J12" s="3" t="b">
         <v>1</v>
@@ -4073,36 +4143,36 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>v42</t>
+          <t>v49</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Delinquent and Health-Risk Behaviors</t>
+          <t>Perceived Effectiveness of School-based Digital/Technology Learning</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Delinquency / Risk Behavior</t>
+          <t>Online / Digital Life</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>-0.0859</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>1.912075681691709</v>
+      </c>
+      <c r="G13" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="E13" s="3" t="n">
-        <v>0.0959</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>1.818492111650485</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>10</v>
-      </c>
       <c r="H13" s="3" t="n">
-        <v>0.08599999999999999</v>
+        <v>-0.0501</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>3.907847503067205</v>
+        <v>2.255537547271746</v>
       </c>
       <c r="J13" s="3" t="b">
         <v>1</v>
@@ -4111,43 +4181,119 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>v49</t>
+          <t>v42</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Perceived Effectiveness of School-based Digital/Technology Learning</t>
+          <t>Delinquent and Health-Risk Behaviors</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Online / Digital Life</t>
+          <t>Delinquency / Risk Behavior</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>-0.09429999999999999</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1.788152305825243</v>
+        <v>1.903171953255426</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>-0.0513</v>
+        <v>0.0861</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>2.331076475666833</v>
+        <v>3.876283090221502</v>
       </c>
       <c r="J14" s="3" t="b">
         <v>1</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>v34</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Physical/Offline Bullying Victimization</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Bullying / Victimization</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0.07829999999999999</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>1.742904841402337</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>0.0654</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>2.944354403025392</v>
+      </c>
+      <c r="J15" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>v40</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Cyberbullying Perpetration (including Misinformation-related)</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Bullying / Victimization</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>0.0562</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>1.250973845297718</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>0.0452</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>2.034936070592473</v>
+      </c>
+      <c r="J16" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J14"/>
+  <autoFilter ref="A1:J16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
